--- a/pinterest-pins-生活/pinterest-生活.xlsx
+++ b/pinterest-pins-生活/pinterest-生活.xlsx
@@ -1479,15 +1479,50 @@
       <c r="Z17" s="3" t="n"/>
     </row>
     <row r="18" ht="15.75" customHeight="1" s="15">
-      <c r="A18" s="4" t="n"/>
-      <c r="B18" s="5" t="n"/>
-      <c r="C18" s="6" t="n"/>
-      <c r="D18" s="6" t="n"/>
-      <c r="E18" s="3" t="n"/>
-      <c r="F18" s="6" t="n"/>
-      <c r="G18" s="6" t="n"/>
-      <c r="H18" s="6" t="n"/>
-      <c r="I18" s="6" t="n"/>
+      <c r="A18" s="4">
+        <f>DATE(2026,9,11)+INT((ROW()-ROW($A$2))/2)</f>
+        <v/>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>21:00〜21:30</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-10_ヒートショック対策は入浴前から上がるまでの手順で決まる</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>https://nevora-lifestyle.vercel.app/posts/2026-10-10_%E3%83%92%E3%83%BC%E3%83%88%E3%82%B7%E3%83%A7%E3%83%83%E3%82%AF%E5%AF%BE%E7%AD%96%E3%81%AF%E5%85%A5%E6%B5%B4%E5%89%8D%E3%81%8B%E3%82%89%E4%B8%8A%E3%81%8C%E3%82%8B%E3%81%BE%E3%81%A7%E3%81%AE%E6%89%8B%E9%A0%86%E3%81%A7%E6%B1%BA%E3%81%BE%E3%82%8B</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>未投稿</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>暮らしの知恵</t>
+        </is>
+      </c>
+      <c r="G18" s="6" t="inlineStr">
+        <is>
+          <t>暮らしの知恵</t>
+        </is>
+      </c>
+      <c r="H18" s="6" t="inlineStr">
+        <is>
+          <t>ヒートショック対策は入浴前から上がるまでの手順で決まる｜脱衣所と浴室の温度の整え方(賃貸でできる範囲つき)</t>
+        </is>
+      </c>
+      <c r="I18" s="6" t="inlineStr">
+        <is>
+          <t>冬の入浴は、暖かい居間から寒い脱衣所へ出る温度差が負担になります。消費者庁の2つの公表資料(令和2年・令和4年公表)をもとに、入る前の暖め方・湯温と時間の目安・上がるときの立ち方を時系列で整理し、賃貸でも工事なしでできる範囲と管理会社に確認する範囲を分けます。 ヒートショックと防災についても、公的データや制度の情報にもとづいて解説しています。 くわしくは「NEVORA|生活を豊かにする総合ガイド」の記事をご覧ください。#暮らしの知恵</t>
+        </is>
+      </c>
       <c r="J18" s="3" t="n"/>
       <c r="K18" s="3" t="n"/>
       <c r="L18" s="3" t="n"/>
